--- a/threagile/output/pasta/risks.xlsx
+++ b/threagile/output/pasta/risks.xlsx
@@ -19,64 +19,64 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>CWE</t>
+  </si>
+  <si>
+    <t>Risk Category</t>
+  </si>
+  <si>
+    <t>Communication Link</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Checked by</t>
+  </si>
+  <si>
+    <t>Likelihood</t>
+  </si>
+  <si>
+    <t>Technical Asset</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>Ticket</t>
   </si>
   <si>
     <t>STRIDE</t>
   </si>
   <si>
-    <t>Impact</t>
-  </si>
-  <si>
-    <t>Risk Category</t>
-  </si>
-  <si>
     <t>RAA %</t>
   </si>
   <si>
     <t>Identified Risk</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
     <t>Mitigation</t>
   </si>
   <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Likelihood</t>
-  </si>
-  <si>
-    <t>Technical Asset</t>
+    <t>Check</t>
   </si>
   <si>
     <t>ID</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Checked by</t>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>CWE</t>
-  </si>
-  <si>
-    <t>Communication Link</t>
-  </si>
-  <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>Justification</t>
   </si>
   <si>
     <t>Elevated</t>
@@ -781,64 +781,64 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B1" s="24" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1" s="24" t="s">
         <v>11</v>
       </c>
       <c r="I1" s="24" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K1" s="24" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="L1" s="24" t="s">
         <v>7</v>
       </c>
       <c r="M1" s="24" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N1" s="24" t="s">
         <v>18</v>
       </c>
       <c r="O1" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="P1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="24" t="s">
+      <c r="Q1" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="R1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="S1" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T1" s="24" t="s">
         <v>13</v>
-      </c>
-      <c r="Q1" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="R1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="S1" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="T1" s="24" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="2">

--- a/threagile/output/pasta/risks.xlsx
+++ b/threagile/output/pasta/risks.xlsx
@@ -10,75 +10,75 @@
     <sheet name="VaultNote Threat Model" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'VaultNote Threat Model'!$A$1:$T$6</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'VaultNote Threat Model'!$A$1:$T$13</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+  <si>
+    <t>Identified Risk</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Checked by</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>Technical Asset</t>
+  </si>
+  <si>
+    <t>RAA %</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>STRIDE</t>
+  </si>
+  <si>
+    <t>Mitigation</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Likelihood</t>
+  </si>
   <si>
     <t>Impact</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
     <t>CWE</t>
   </si>
   <si>
+    <t>Communication Link</t>
+  </si>
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Ticket</t>
+  </si>
+  <si>
     <t>Risk Category</t>
   </si>
   <si>
-    <t>Communication Link</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Justification</t>
-  </si>
-  <si>
-    <t>Checked by</t>
-  </si>
-  <si>
-    <t>Likelihood</t>
-  </si>
-  <si>
-    <t>Technical Asset</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Ticket</t>
-  </si>
-  <si>
-    <t>STRIDE</t>
-  </si>
-  <si>
-    <t>RAA %</t>
-  </si>
-  <si>
-    <t>Identified Risk</t>
-  </si>
-  <si>
-    <t>Mitigation</t>
-  </si>
-  <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
     <t>Elevated</t>
   </si>
   <si>
@@ -88,6 +88,91 @@
     <t>Medium</t>
   </si>
   <si>
+    <t>Elevation of Privilege</t>
+  </si>
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
+    <t>CWE-693</t>
+  </si>
+  <si>
+    <t>Stage III - Undocumented Application Entry Point</t>
+  </si>
+  <si>
+    <t>AWS API Gateway</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Undocumented Entry Point: AWS API Gateway is internet-exposed but has no entry_point_type declared</t>
+  </si>
+  <si>
+    <t>Document all application entry points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Declare entry_point_type on every internet-exposed technical asset (api, web_ui, cli, file_upload, webhook, cron, or internal_rpc). Maintain an entry point register and review it as part of each release cycle.
+</t>
+  </si>
+  <si>
+    <t>Do all internet-exposed technical assets have an entry_point_type declared?</t>
+  </si>
+  <si>
+    <t>undocumented-entry-point@aws-api-gateway</t>
+  </si>
+  <si>
+    <t>Unchecked</t>
+  </si>
+  <si>
+    <t>AWS ECR Container Registry</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Undocumented Entry Point: AWS ECR Container Registry is internet-exposed but has no entry_point_type declared</t>
+  </si>
+  <si>
+    <t>undocumented-entry-point@container-registry</t>
+  </si>
+  <si>
+    <t>AWS SES</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Undocumented Entry Point: AWS SES is internet-exposed but has no entry_point_type declared</t>
+  </si>
+  <si>
+    <t>undocumented-entry-point@aws-ses</t>
+  </si>
+  <si>
+    <t>GitHub Actions Build Pipeline</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Undocumented Entry Point: GitHub Actions Build Pipeline is internet-exposed but has no entry_point_type declared</t>
+  </si>
+  <si>
+    <t>undocumented-entry-point@build-pipeline</t>
+  </si>
+  <si>
+    <t>VaultNote Source Repository</t>
+  </si>
+  <si>
+    <t>Undocumented Entry Point: VaultNote Source Repository is internet-exposed but has no entry_point_type declared</t>
+  </si>
+  <si>
+    <t>undocumented-entry-point@source-repo</t>
+  </si>
+  <si>
     <t>Denial of Service</t>
   </si>
   <si>
@@ -103,10 +188,7 @@
     <t>API Server</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>82</t>
+    <t>44</t>
   </si>
   <si>
     <t>Missing Per-Operation Rate Limiting: custom service API Server processes auth data with unthrottled outgoing communication links</t>
@@ -126,13 +208,10 @@
     <t>per-operation-rate-limiting-missing@api-server</t>
   </si>
   <si>
-    <t>Unchecked</t>
-  </si>
-  <si>
     <t>Browser SPA</t>
   </si>
   <si>
-    <t>54</t>
+    <t>29</t>
   </si>
   <si>
     <t>Missing Per-Operation Rate Limiting: custom service Browser SPA processes auth data with unthrottled outgoing communication links</t>
@@ -150,7 +229,7 @@
     <t>Nginx Reverse Proxy</t>
   </si>
   <si>
-    <t>2</t>
+    <t>1</t>
   </si>
   <si>
     <t>No Rate Limiting: internet-exposed API Nginx Reverse Proxy has communication links without rate limiting</t>
@@ -186,53 +265,102 @@
     <t>VAULT-120</t>
   </si>
   <si>
+    <t>Spoofing</t>
+  </si>
+  <si>
+    <t>CWE-287</t>
+  </si>
+  <si>
+    <t>Stage VI - Weak Authentication Strength on Internet-Exposed Entry Point</t>
+  </si>
+  <si>
+    <t>LLM Note Summarizer</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Weak Authentication: internet-exposed entry point LLM Note Summarizer lacks strong authentication for confidential data</t>
+  </si>
+  <si>
+    <t>Strengthen authentication on all internet-exposed entry points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Require MFA for all user-facing internet entry points handling sensitive data. Declare requires_authentication_strength as mfa or hardware on the technical asset. Consider phishing-resistant authentication (WebAuthn, FIDO2) for high-value assets.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do all internet-exposed entry points with confidential or higher data have requires_authentication_strength set to mfa or hardware?
+</t>
+  </si>
+  <si>
+    <t>weak-auth-on-entry-point@llm-summarizer</t>
+  </si>
+  <si>
+    <t>Very High</t>
+  </si>
+  <si>
+    <t>Information Disclosure</t>
+  </si>
+  <si>
+    <t>CWE-284</t>
+  </si>
+  <si>
+    <t>Stage VII - Internet-Reachable Datastore With No Mitigation</t>
+  </si>
+  <si>
+    <t>Internet-Reachable Datastore: AWS ECR Container Registry can be reached from an internet-exposed asset with no application-tier separation</t>
+  </si>
+  <si>
+    <t>Segment datastores from internet-facing components</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place all datastores in a dedicated backend trust boundary with no direct internet access. Ensure all communication links between internet-facing assets and datastores go through the application tier (no direct datastore exposure). Apply defense-in-depth with connection-level authentication and network ACLs.
+</t>
+  </si>
+  <si>
+    <t>Are all datastores behind at least one application-tier trust boundary?</t>
+  </si>
+  <si>
+    <t>internet-reachable-datastore@container-registry</t>
+  </si>
+  <si>
+    <t>VaultNote Vector Store</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Internet-Reachable Datastore: VaultNote Vector Store can be reached from an internet-exposed asset with no application-tier separation</t>
+  </si>
+  <si>
+    <t>internet-reachable-datastore@vector-store</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
     <t>Unlikely</t>
   </si>
   <si>
-    <t>Tampering</t>
-  </si>
-  <si>
-    <t>Development</t>
-  </si>
-  <si>
-    <t>CWE-693</t>
-  </si>
-  <si>
-    <t>Stage II - Custom-Developed Asset With No Build Pipeline Security</t>
-  </si>
-  <si>
-    <t>No Build Pipeline Security: custom-developed asset API Server has no SAST or dependency scanning</t>
-  </si>
-  <si>
-    <t>Add SAST and dependency scanning to the CI/CD pipeline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrate static analysis (e.g., Semgrep, SonarQube, CodeQL) and dependency scanning (e.g., Dependabot, OWASP Dependency-Check) into the build pipeline for every custom-developed asset. Fail builds on high-severity findings.
+    <t>Stage I - No Threat Scenarios Defined for Internet-Exposed Entry Points</t>
+  </si>
+  <si>
+    <t>Missing Threat Scenario: internet entry point LLM Note Summarizer has no documented threat scenario</t>
+  </si>
+  <si>
+    <t>Define threat scenarios for all internet-exposed entry points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add a threat_scenarios section to the model with at least one scenario per distinct threat actor type (e.g., script-kiddie, insider, nation-state). Each scenario should document entry_assets, kill_chain_steps, and mitigated_by controls.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Does every custom-developed technical asset have a build pipeline with SAST and dependency scanning?
+    <t xml:space="preserve">Does the model have at least one threat_scenarios entry for each internet-facing entry point?
 </t>
   </si>
   <si>
-    <t>custom-development-no-sast@api-server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAST tooling (Semgrep with Node.js ruleset) is integrated into the GitHub Actions pipeline but the full security rule set is not yet enabled. Remaining rule categories (injection, secrets, SSRF) are being evaluated for false-positive rates. Target: sprint 21.
-</t>
-  </si>
-  <si>
-    <t>VAULT-121</t>
-  </si>
-  <si>
-    <t>No Build Pipeline Security: custom-developed asset Browser SPA has no SAST or dependency scanning</t>
-  </si>
-  <si>
-    <t>custom-development-no-sast@browser-spa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same Semgrep pipeline as api-server covers the React SPA source. ESLint security plugin (eslint-plugin-security) is configured but not yet enforced as a blocking check. Planned for sprint 21.
-</t>
+    <t>missing-threat-scenario@llm-summarizer</t>
   </si>
 </sst>
 </file>
@@ -760,15 +888,15 @@
   <cols>
     <col customWidth="true" max="1" min="1" width="15"/>
     <col customWidth="true" max="2" min="2" width="17"/>
-    <col customWidth="true" max="3" min="3" width="13"/>
-    <col customWidth="true" max="4" min="4" width="21.285714285714285"/>
-    <col customWidth="true" max="5" min="5" width="16.142857142857142"/>
+    <col customWidth="true" max="3" min="3" width="14.428571428571429"/>
+    <col customWidth="true" max="4" min="4" width="25.57142857142857"/>
+    <col customWidth="true" max="5" min="5" width="17"/>
     <col customWidth="true" max="6" min="6" width="12.714285714285714"/>
-    <col customWidth="true" max="7" min="7" width="66.71428571428571"/>
-    <col customWidth="true" max="8" min="8" width="23"/>
+    <col customWidth="true" max="7" min="7" width="67.57142857142857"/>
+    <col customWidth="true" max="8" min="8" width="31.57142857142857"/>
     <col customWidth="true" max="9" min="9" width="25"/>
     <col customWidth="true" max="10" min="10" width="12"/>
-    <col customWidth="true" max="11" min="11" width="98.57142857142857"/>
+    <col customWidth="true" max="11" min="11" width="75"/>
     <col customWidth="true" max="12" min="12" width="77.85714285714286"/>
     <col customWidth="true" max="13" min="13" width="75"/>
     <col customWidth="true" max="15" min="14" width="40"/>
@@ -781,64 +909,64 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="R1" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="S1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="N1" s="24" t="s">
+      <c r="T1" s="24" t="s">
         <v>18</v>
-      </c>
-      <c r="O1" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="P1" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="R1" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S1" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="T1" s="24" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2">
@@ -973,7 +1101,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>23</v>
@@ -985,174 +1113,608 @@
         <v>25</v>
       </c>
       <c r="G4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="K4" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="18" t="s">
+      <c r="L4" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="K4" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="M4" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N4" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="O4" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="P4" s="12" t="s">
-        <v>49</v>
+      <c r="P4" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="S4" s="17" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="T4" s="16" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="7" t="s">
+      <c r="D5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J5" s="18" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="M5" s="23" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="N5" s="23" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="O5" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="P5" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="Q5" s="19" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="R5" s="17" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="S5" s="17" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="T5" s="16" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="D6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="O6" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="P6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q6" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R6" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="S6" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T6" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="H7" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="O7" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q7" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R7" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="S7" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T7" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="D8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="L8" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="M8" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="O8" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="P8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q8" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R8" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="S8" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T8" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="L9" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="N9" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="O9" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="P9" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q9" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="R9" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="S9" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="T9" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="L10" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="M10" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="N10" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="O10" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="P10" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q10" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R10" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="S10" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T10" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="18" t="s">
+      <c r="I11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="L6" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="M6" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="N6" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="O6" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="P6" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q6" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="R6" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="S6" s="17" t="s">
+      <c r="K11" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="L11" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="M11" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="N11" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="O11" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="P11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q11" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R11" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="S11" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T11" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="L12" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="M12" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="N12" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="O12" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="P12" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q12" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R12" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="S12" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T12" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="T6" s="16" t="s">
-        <v>65</v>
+      <c r="F13" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="L13" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="M13" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="N13" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="O13" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="P13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q13" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R13" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="S13" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T13" s="16" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$T$6"/>
+  <autoFilter ref="$A$1:$T$13"/>
   <pageSetup orientation="landscape" paperSize="9"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;P</oddHeader>

--- a/threagile/output/pasta/risks.xlsx
+++ b/threagile/output/pasta/risks.xlsx
@@ -17,66 +17,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
+  <si>
+    <t>STRIDE</t>
+  </si>
+  <si>
+    <t>Risk Category</t>
+  </si>
+  <si>
+    <t>Communication Link</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Likelihood</t>
+  </si>
+  <si>
+    <t>CWE</t>
+  </si>
+  <si>
+    <t>Mitigation</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Ticket</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Technical Asset</t>
+  </si>
   <si>
     <t>Identified Risk</t>
   </si>
   <si>
-    <t>Action</t>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>RAA %</t>
   </si>
   <si>
     <t>Checked by</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>Technical Asset</t>
-  </si>
-  <si>
-    <t>RAA %</t>
-  </si>
-  <si>
-    <t>Justification</t>
-  </si>
-  <si>
-    <t>STRIDE</t>
-  </si>
-  <si>
-    <t>Mitigation</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Likelihood</t>
-  </si>
-  <si>
-    <t>Impact</t>
-  </si>
-  <si>
-    <t>CWE</t>
-  </si>
-  <si>
-    <t>Communication Link</t>
-  </si>
-  <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Ticket</t>
-  </si>
-  <si>
-    <t>Risk Category</t>
   </si>
   <si>
     <t>Elevated</t>
@@ -125,7 +125,20 @@
     <t>undocumented-entry-point@aws-api-gateway</t>
   </si>
   <si>
-    <t>Unchecked</t>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entry-point inventory: documenting the CI/CD webhooks, SES sending endpoint, registry, and API Gateway as reviewed entry points with owners in the architecture record.
+</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>Security Team</t>
+  </si>
+  <si>
+    <t>VAULT-171</t>
   </si>
   <si>
     <t>AWS ECR Container Registry</t>
@@ -208,6 +221,13 @@
     <t>per-operation-rate-limiting-missing@api-server</t>
   </si>
   <si>
+    <t xml:space="preserve">Per-route rate limits (login, note-create, share endpoints) at nginx and API Gateway usage plans; complements the existing global limiter.
+</t>
+  </si>
+  <si>
+    <t>VAULT-146</t>
+  </si>
+  <si>
     <t>Browser SPA</t>
   </si>
   <si>
@@ -249,9 +269,6 @@
     <t>no-rate-limiting-public-api@nginx-proxy</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rate limiting via nginx limit_req_zone is planned for sprint 21. Current mitigation: account lockout after 10 failed login attempts implemented in the API layer. Full IP-level rate limiting is a VAULT-120 blocker before production launch.
 </t>
   </si>
@@ -259,9 +276,6 @@
     <t>2026-04-25</t>
   </si>
   <si>
-    <t>Security Team</t>
-  </si>
-  <si>
     <t>VAULT-120</t>
   </si>
   <si>
@@ -297,6 +311,46 @@
     <t>weak-auth-on-entry-point@llm-summarizer</t>
   </si>
   <si>
+    <t xml:space="preserve">The summarizer's unauthenticated internet exposure is one of the model's intentional misconfigurations; remediation (service token + gateway routing) is the same effort as the already-tracked ai-ml-inference-endpoint-no-auth finding.
+</t>
+  </si>
+  <si>
+    <t>VAULT-130</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Unlikely</t>
+  </si>
+  <si>
+    <t>Stage I - No Threat Scenarios Defined for Internet-Exposed Entry Points</t>
+  </si>
+  <si>
+    <t>Missing Threat Scenario: internet entry point LLM Note Summarizer has no documented threat scenario</t>
+  </si>
+  <si>
+    <t>Define threat scenarios for all internet-exposed entry points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add a threat_scenarios section to the model with at least one scenario per distinct threat actor type (e.g., script-kiddie, insider, nation-state). Each scenario should document entry_assets, kill_chain_steps, and mitigated_by controls.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the model have at least one threat_scenarios entry for each internet-facing entry point?
+</t>
+  </si>
+  <si>
+    <t>missing-threat-scenario@llm-summarizer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A PASTA threat scenario covering LLM endpoint abuse (prompt injection, cost amplification) is being added to feature_threats.yaml.
+</t>
+  </si>
+  <si>
+    <t>VAULT-172</t>
+  </si>
+  <si>
     <t>Very High</t>
   </si>
   <si>
@@ -325,6 +379,13 @@
     <t>internet-reachable-datastore@container-registry</t>
   </si>
   <si>
+    <t>False Positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECR repositories are private (no public registry policy); the asset's internet flag models the managed-service endpoint, not public readability. Pull/push require AWS IAM auth.
+</t>
+  </si>
+  <si>
     <t>VaultNote Vector Store</t>
   </si>
   <si>
@@ -337,30 +398,8 @@
     <t>internet-reachable-datastore@vector-store</t>
   </si>
   <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Unlikely</t>
-  </si>
-  <si>
-    <t>Stage I - No Threat Scenarios Defined for Internet-Exposed Entry Points</t>
-  </si>
-  <si>
-    <t>Missing Threat Scenario: internet entry point LLM Note Summarizer has no documented threat scenario</t>
-  </si>
-  <si>
-    <t>Define threat scenarios for all internet-exposed entry points</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add a threat_scenarios section to the model with at least one scenario per distinct threat actor type (e.g., script-kiddie, insider, nation-state). Each scenario should document entry_assets, kill_chain_steps, and mitigated_by controls.
+    <t xml:space="preserve">The vector store is modeled with internet: false inside the AI Services trust boundary; the PASTA rule flags it through the internet-facing LLM-summarizer caller, not through actual exposure. Network policy restricts ingress to the RAG pipeline and summarizer.
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Does the model have at least one threat_scenarios entry for each internet-facing entry point?
-</t>
-  </si>
-  <si>
-    <t>missing-threat-scenario@llm-summarizer</t>
   </si>
 </sst>
 </file>
@@ -369,149 +408,127 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <fonts count="23">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FFFF2600"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FFFF2600"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
-      <color rgb="FFFF2600"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FFA0281E"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FFA0281E"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
-      <color rgb="FFA0281E"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FFFF8E00"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FFFF8E00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
-      <color rgb="FFFF8E00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FFC87832"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FFC87832"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
-      <color rgb="FFC87832"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FF23465F"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FF23465F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
-      <color rgb="FF23465F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <family val="2"/>
+      <color rgb="FF008F00"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <color rgb="FF0000FF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <color rgb="FFFF40FF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <color rgb="FFFF9300"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <color rgb="FF666666"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FF008F00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF40FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF9300"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF666666"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF008F00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="1"/>
       <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -900,7 +917,7 @@
     <col customWidth="true" max="12" min="12" width="77.85714285714286"/>
     <col customWidth="true" max="13" min="13" width="75"/>
     <col customWidth="true" max="15" min="14" width="40"/>
-    <col customWidth="true" max="16" min="16" width="16.142857142857142"/>
+    <col customWidth="true" max="16" min="16" width="18.714285714285715"/>
     <col customWidth="true" max="17" min="17" width="80"/>
     <col customWidth="true" max="18" min="18" width="15.285714285714285"/>
     <col customWidth="true" max="19" min="19" width="17.857142857142854"/>
@@ -909,64 +926,64 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>12</v>
       </c>
       <c r="D1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="24" t="s">
         <v>8</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="M1" s="24" t="s">
-        <v>9</v>
       </c>
       <c r="N1" s="24" t="s">
         <v>15</v>
       </c>
       <c r="O1" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="R1" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q1" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="R1" s="24" t="s">
-        <v>10</v>
-      </c>
       <c r="S1" s="24" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="T1" s="24" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2">
@@ -1015,20 +1032,20 @@
       <c r="O2" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="12" t="s">
         <v>35</v>
       </c>
       <c r="Q2" s="19" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="R2" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T2" s="16" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -1054,16 +1071,16 @@
         <v>26</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K3" s="19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L3" s="23" t="s">
         <v>31</v>
@@ -1075,22 +1092,22 @@
         <v>33</v>
       </c>
       <c r="O3" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="P3" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="S3" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="T3" s="16" t="s">
         <v>39</v>
-      </c>
-      <c r="P3" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q3" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="R3" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="S3" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -1116,16 +1133,16 @@
         <v>26</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K4" s="19" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L4" s="23" t="s">
         <v>31</v>
@@ -1137,22 +1154,22 @@
         <v>33</v>
       </c>
       <c r="O4" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="P4" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="P4" s="12" t="s">
         <v>35</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S4" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T4" s="16" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
@@ -1178,16 +1195,16 @@
         <v>26</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J5" s="18" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L5" s="23" t="s">
         <v>31</v>
@@ -1199,22 +1216,22 @@
         <v>33</v>
       </c>
       <c r="O5" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="P5" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="P5" s="12" t="s">
         <v>35</v>
       </c>
       <c r="Q5" s="19" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="R5" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S5" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T5" s="16" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
@@ -1240,16 +1257,16 @@
         <v>26</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L6" s="23" t="s">
         <v>31</v>
@@ -1261,22 +1278,22 @@
         <v>33</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="P6" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="P6" s="12" t="s">
         <v>35</v>
       </c>
       <c r="Q6" s="19" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="R6" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S6" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T6" s="16" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -1290,55 +1307,55 @@
         <v>22</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K7" s="19" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M7" s="23" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="N7" s="23" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="P7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="P7" s="12" t="s">
         <v>35</v>
       </c>
       <c r="Q7" s="19" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="R7" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S7" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T7" s="16" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
@@ -1352,55 +1369,55 @@
         <v>22</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J8" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="L8" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="K8" s="19" t="s">
+      <c r="N8" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="L8" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="M8" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="N8" s="23" t="s">
-        <v>60</v>
-      </c>
       <c r="O8" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P8" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="P8" s="12" t="s">
         <v>35</v>
       </c>
       <c r="Q8" s="19" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="R8" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S8" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T8" s="16" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
@@ -1411,58 +1428,58 @@
         <v>21</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="M9" s="23" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="N9" s="23" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="Q9" s="19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="R9" s="17" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="S9" s="17" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="T9" s="16" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -1473,241 +1490,241 @@
         <v>21</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="M10" s="23" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="N10" s="23" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="O10" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="P10" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="P10" s="12" t="s">
         <v>35</v>
       </c>
       <c r="Q10" s="19" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="R10" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S10" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I11" s="5" t="s">
+      <c r="A11" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="I11" s="9" t="s">
         <v>28</v>
       </c>
       <c r="J11" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="L11" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="M11" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="N11" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="O11" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="P11" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q11" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="R11" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="K11" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="L11" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="M11" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="N11" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="O11" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="P11" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q11" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="R11" s="17" t="s">
-        <v>28</v>
-      </c>
       <c r="S11" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T11" s="16" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="C12" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="I12" s="5" t="s">
+      <c r="F12" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" s="21" t="s">
         <v>28</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="L12" s="23" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="M12" s="23" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="N12" s="23" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="O12" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="P12" s="10" t="s">
-        <v>35</v>
+        <v>114</v>
+      </c>
+      <c r="P12" s="15" t="s">
+        <v>115</v>
       </c>
       <c r="Q12" s="19" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="R12" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S12" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T12" s="16" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="I13" s="9" t="s">
+      <c r="A13" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="I13" s="21" t="s">
         <v>28</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M13" s="23" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="N13" s="23" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O13" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="P13" s="10" t="s">
-        <v>35</v>
+        <v>120</v>
+      </c>
+      <c r="P13" s="15" t="s">
+        <v>115</v>
       </c>
       <c r="Q13" s="19" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="R13" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S13" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T13" s="16" t="s">
         <v>28</v>
